--- a/resultados/Fiscalizacion_Web_DM_jeringas-hipodermicas_03-09-2026.xlsx
+++ b/resultados/Fiscalizacion_Web_DM_jeringas-hipodermicas_03-09-2026.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hallazgos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Búsquedas Marketplace" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anexo — sobre el tope" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Búsquedas Marketplace" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,11 +39,11 @@
       <color rgb="00A11B1B"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="001E6B1E"/>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,11 +68,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF6CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D7F0D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,9 +114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -562,22 +556,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jeringa 20 ml Luer Lock (sin marca declarada)</t>
+          <t>Jeringa 20ml Luer Slip 21G x 1½ Jumala – Embalaje 800 Unidades</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://medcare.cl/products/jeringa-20-ml-sin-aguja</t>
+          <t>https://www.importadoraamg.cl/jeringa-20ml-luer-slip-21-x-12-jumala-embalaje-800-unidades-16-paquetes-x-50-unidades</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Jeringa 20 ml - Luer Lock</t>
+          <t>Jeringa 20ml Luer Slip 21G x 1½ Jumala – Embalaje 800 Unidades (16 Paquetes x 50 Unidades)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Medcare (medcare.cl)</t>
+          <t>Importadora AMG (Santiago, Renca)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -594,7 +588,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>La publicación no declara marca ni fabricante, solo volumen y tipo de conexión. Sin marca no hay forma de cruzar contra el listado ISP. Precio $490. Requiere verificación por imagen del envase antes de resolver.</t>
+          <t>Marca 'Jumala' no figura en el listado ISP de jeringas hipodérmicas vigente (15-04-2026). Venta directa por importador con dirección y teléfono chilenos. Misma marca detectada en 3 publicaciones de Mercado Libre Chile no accesibles por bloqueo 403 (ver hoja Búsquedas Marketplace).</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr"/>
@@ -603,31 +597,39 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Jeringa desechable sin aguja, punta excéntrica (sin marca declarada)</t>
+          <t>Jeringa Desechable con Aguja Luer Lock 5ML - Caja 100 unidades CRANBERRY</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>https://prosaludortopedia.cl/jeringa-desechable-sin-aguja-punta-excentrica</t>
+          <t>https://lacasadelguante.cl/products/jeringa-desechable-con-aguja-luer-lock-5ml-caja-100-unidades-cranberry</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Jeringa desechable sin aguja punta excéntrica</t>
+          <t>Jeringa Desechable con Aguja Luer Lock 5ML - Caja 100 unidades CRANBERRY</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ProSalud Ortopedia (prosaludortopedia.cl)</t>
+          <t>La Casa del Guante (Huechuraba)</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>CRANBERRY (Reutter S.A.)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Ninguno cubre 5 mL</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>NO REGISTRADO</t>
@@ -635,7 +637,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Indicada para alimentación por sonda. No declara marca, fabricante ni precio; venta por cantidad mínima de 10 y máxima de 25 unidades, posiblemente mayorista. Sin marca no hay forma de cruzar contra el listado ISP. Requiere verificación por imagen del envase.</t>
+          <t>La marca CRANBERRY (titular Reutter S.A.) SÍ figura en el listado ISP, pero únicamente con registros para 20 mL y 60 mL (DM 493/20, DM 524/21, DM 525/21, DM 531/21, DM 532/21, DM 624/24, DM 625/24). Ningún registro Cranberry ampara la presentación de 5 mL ofertada aquí: la marca coincide pero la presentación no está cubierta. Verificar con app móvil ISP antes de descartar, ya que el 27-08 el inspector confirmó registro para otras unidades de 3/5/10cc 'Cranberry' citando un registro (DM 399/15) que no aparece en el Excel ISP vigente cargado en esta corrida; se deja constancia de la discrepancia para que el inspector la resuelva con la fuente autoritativa.</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr"/>
@@ -644,47 +646,47 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Jeringa 20cc Sin Aguja Nedflex, Luer Lock</t>
+          <t>Cranberry Jeringa Desechable 10ml 1 Unidad</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://dipromed.cl/jeringas-hipodermica-/200-jeringa-20-cc-sin-aguja.html</t>
+          <t>https://www.mercadofarma.cl/products/copia-de-jeringa-desechable-20ml</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Jeringa 20 cc Sin Aguja Nedflex</t>
+          <t>Cranberry Jeringa Desechable 10ml 1 Unidad</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Dipromed (dipromed.cl)</t>
+          <t>Mercado Farma</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>SÍ</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>NEDFLEX (Jeringa Hipodérmica, estéril, para un solo uso, Luer Lock)</t>
+          <t>CRANBERRY (Reutter S.A.)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>DM 416/16</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
+          <t>Ninguno cubre 10 mL</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>DM 416/16 ampara 3, 5, 10, 20 y 60 mL en Luer Lock: la presentación de 20cc Luer Lock ofertada está cubierta. El mismo producto también se ofrece en Luer Slip, amparado por DM 456/18.</t>
+          <t>Misma situación que el hallazgo de La Casa del Guante: marca CRANBERRY presente en el listado ISP solo para 20 mL y 60 mL. La presentación de 10 mL ofertada no está amparada por ningún registro Cranberry vigente en el Excel cargado. Ver nota sobre discrepancia con 'DM 399/15' citado en revisión previa del inspector.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr"/>
@@ -693,47 +695,39 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Jeringa BD Luer Lock 20 ml sin aguja, caja 250 unidades</t>
+          <t>Jeringa Desechable Nº20 (display, venta por mayor)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://vidamedica.cl/productos/jeringa-bd-luer-lock-20-ml-sin-aguja-caja-250-unidades/</t>
+          <t>https://comercioelsol.cl/product/jeringa-desechable-no20-display-349-x-mayor/</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Jeringa BD Luer Lock 20 ml sin aguja - Caja 250 unidades</t>
+          <t>JERINGA DESECHABLE Nº20 DISPLAY $349 X MAYOR</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Vidamedica (vidamedica.cl)</t>
+          <t>Comercio El Sol</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>BECTON DICKINSON (Jeringas Hipodérmicas para un uso Punta Luer Lock)</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>DM/10JE/0194/09</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Marca Becton Dickinson declarada explícitamente. El registro ampara 20mL y 30mL en punta Luer Lock: la presentación ofertada (20 ml) está cubierta. Precio $65.100.</t>
+          <t>Sin marca ni fabricante visible en la publicación. Tienda general (categoría 'Remedios'), no especializada en insumos médicos, con venta al detalle y por mayor. Título genérico impide identificar fabricante; no se encontraron imágenes con texto de marca en el contenido accesible.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
@@ -742,47 +736,39 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Jeringa Luer Lock 50 ml Sin Aguja Muncare, caja 25 unidades</t>
+          <t>Jeringa Desechable Luer Slip 5cc 21G x 1½ (color cranberry, sin marca de fabricante)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://geerdink.cl/products/jeringa-luer-lock-desechable-muncare-50-ml-sin-aguja-pack-x-25</t>
+          <t>https://medpro360.cl/tienda/jeringa-desechable-100-uni/</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Jeringa Desechable Luer Lock 50 Ml Sin Aguja caja x 25 Unds. Muncare</t>
+          <t>Jeringa Desechable – MedPro360</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Geerdink (geerdink.cl)</t>
+          <t>MedPro360 (Concepción)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>MUNCARE (Jeringas Hipodérmicas para un uso, Luer Lock)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>DM 400/15</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>DM 400/15 ampara 3, 5, 10, 20 y 50 mL en Luer Lock: la presentación de 50 mL ofertada está cubierta. Precio $11.690.</t>
+          <t>La publicación no identifica marca ni fabricante; 'cranberry' se usa como denominación del color del conector Luer Slip, no como marca comercial (confirmado en el texto de la ficha). Se aclara esto porque en corridas previas se confundió el color 'cranberry' de conectores genéricos con la marca registrada CRANBERRY de Reutter S.A.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
@@ -791,47 +777,39 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Jeringa 20 mL sin aguja Luer Lock Cranberry, caja 50 unidades</t>
+          <t>Jeringa desechable con aguja 5 mL (sin marca)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://www.traqueo.cl/tienda/insumos/jeringa-20-ml-sin-aguja-luer-lock/</t>
+          <t>https://www.drsimi.cl/cranberry-jeringa-5-ml-aguja-21-g-x-1-1-2-1-pieza/p</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Jeringa 20 mL sin aguja (Luer Lock) | Estéril Cranberry</t>
+          <t>Jeringa desechable con aguja 5 mL 1 unidad</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Traqueo (traqueo.cl)</t>
+          <t>Farmacias del Dr. Simi Chile</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>CRANBERRY (Jeringa hipodérmica, sin aguja, estéril, para un solo uso, luer lock)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>DM 624/24</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Marca Cranberry declarada explícitamente. DM 624/24 ampara exactamente 20mL Luer Lock sin aguja. Precio $9.500, caja de 50 unidades.</t>
+          <t>El slug de la URL contiene 'cranberry' pero el título, descripción y ficha del producto no mencionan marca ni fabricante; se confirmó que no es la marca comercial CRANBERRY (Reutter S.A.). Venta por unidad a público general.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
@@ -840,54 +818,504 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Jeringa Sin Aguja Catéter 60ml (marca comercial Reutter)</t>
+          <t>Jeringa desechable con aguja 10 mL (sin marca)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://farmaciaelquimico.cl/products/jeringa-sin-aguja-cateter-60ml</t>
+          <t>https://www.drsimi.cl/cranberry-jeringa-10-ml-aguja-21-g-x-1-1-2-1-pieza/p</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Jeringa Sin Aguja Cateter 60ml</t>
+          <t>Jeringa desechable con aguja 10 mL 1 unidad</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Farmacia El Químico (farmaciaelquimico.cl)</t>
+          <t>Farmacias del Dr. Simi Chile</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>CRANBERRY (Jeringa hipodérmica, estéril, para un uso, Punta Catéter)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>DM 531/21</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>La publicación declara marca «Reutter», que no figura en el listado. Reutter S.A. es distribuidor de la marca Cranberry (confirmado en otra fiscalización de esta misma sesión, categoría guantes quirúrgicos), y DM 531/21 ampara exactamente 60mL punta catéter. Es muy probable que el producto real sea Cranberry. VERIFICAR EL ENVASE por imagen antes de resolver: es el mismo patrón de «Reutter = distribuidor, no fabricante» detectado el 02-09-2026. Precio $990.</t>
+          <t>Sin marca ni fabricante mencionados en título ni descripción. Venta por unidad a público general, mismo vendedor que el hallazgo anterior de 5 mL.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa desechable 5 mL 21G (Importado, sin marca)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://tienda.tclgroup.cl/product/jeringa-desechable-5-ml-21g/</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa desechable 5 mL | 21G</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>TCL Group</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Producto categorizado solo como 'Importado', sin marca ni fabricante identificable en la ficha.</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Pack 100 Jeringa Venotek Desechable Luer Lock 5CC 21G x 1 1/2</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://simple.ripley.cl/pack-100-jeringa-venotek-desechable-luer-lock-5cc-21-gr-x1-12-mpm10001511831</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>PACK 100 JERINGA VENOTEK DESECHABLE LUER LOCK 5CC 21 GR X1 1/2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Ripley Chile</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>VENOTEK (Tecnika S.A.)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Ninguno cubre 5 mL (DM 578/22 solo ampara 60 mL Luer Lock)</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>La marca VENOTEK figura en el listado ISP, pero con un único registro (DM 578/22) que ampara exclusivamente la presentación de 60 mL, Luer Lock. La presentación ofertada aquí es de 5CC (5 mL), fuera del alcance de ese registro. Caso análogo al de la aguja Pentapoint 32G que motivó la regla de verificar presentación, no solo marca.</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa Hipodérmica con aguja marca Prosyr 60 mL 21G x 1½</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.osm.cl/product-page/jeringa-hipod%C3%A9rmica-prosyr-60-ml-21g-x1-1-2-unidad</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa 60ml 21G Prosyr</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>OSM Ltda.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Marca 'Prosyr' no figura en el listado ISP de jeringas hipodérmicas vigente. Producto figura agotado al momento de la consulta; se incluye igual porque la publicación sigue activa y puede reabastecerse.</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa 20 ml Luer Lock (sin marca declarada)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>https://medcare.cl/products/jeringa-20-ml-sin-aguja</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa 20 ml - Luer Lock</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Medcare (medcare.cl)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>[Pasada complementaria del 11-09-2026] La publicación no declara marca ni fabricante, solo volumen y tipo de conexión. Sin marca no hay forma de cruzar contra el listado ISP. Precio $490. Requiere verificación por imagen del envase antes de resolver.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa desechable sin aguja, punta excéntrica (sin marca declarada)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>https://prosaludortopedia.cl/jeringa-desechable-sin-aguja-punta-excentrica</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa desechable sin aguja punta excéntrica</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>ProSalud Ortopedia (prosaludortopedia.cl)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>[Pasada complementaria del 11-09-2026] Indicada para alimentación por sonda. No declara marca, fabricante ni precio; venta por cantidad mínima de 10 y máxima de 25 unidades, posiblemente mayorista. Sin marca no hay forma de cruzar contra el listado ISP. Requiere verificación por imagen del envase.</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa 20cc Sin Aguja Nedflex, Luer Lock</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>https://dipromed.cl/jeringas-hipodermica-/200-jeringa-20-cc-sin-aguja.html</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa 20 cc Sin Aguja Nedflex</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Dipromed (dipromed.cl)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>NEDFLEX (Jeringa Hipodérmica, estéril, para un solo uso, Luer Lock)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>DM 416/16</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>[Pasada complementaria del 11-09-2026] Ojo: posible mismo producto que la fila del anexo (dipromed.cl/medicina/200-277-jeringa-20-cc-sin-aguja.html), publicado bajo otra ruta del mismo sitio. Verificar antes de contar dos veces. DM 416/16 ampara 3, 5, 10, 20 y 60 mL en Luer Lock: la presentación de 20cc Luer Lock ofertada está cubierta. El mismo producto también se ofrece en Luer Slip, amparado por DM 456/18.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa BD Luer Lock 20 ml sin aguja, caja 250 unidades</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>https://vidamedica.cl/productos/jeringa-bd-luer-lock-20-ml-sin-aguja-caja-250-unidades/</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa BD Luer Lock 20 ml sin aguja - Caja 250 unidades</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Vidamedica (vidamedica.cl)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>BECTON DICKINSON (Jeringas Hipodérmicas para un uso Punta Luer Lock)</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>DM/10JE/0194/09</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>[Pasada complementaria del 11-09-2026] Marca Becton Dickinson declarada explícitamente. El registro ampara 20mL y 30mL en punta Luer Lock: la presentación ofertada (20 ml) está cubierta. Precio $65.100.</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa Luer Lock 50 ml Sin Aguja Muncare, caja 25 unidades</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>https://geerdink.cl/products/jeringa-luer-lock-desechable-muncare-50-ml-sin-aguja-pack-x-25</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa Desechable Luer Lock 50 Ml Sin Aguja caja x 25 Unds. Muncare</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Geerdink (geerdink.cl)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>MUNCARE (Jeringas Hipodérmicas para un uso, Luer Lock)</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>DM 400/15</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>[Pasada complementaria del 11-09-2026] DM 400/15 ampara 3, 5, 10, 20 y 50 mL en Luer Lock: la presentación de 50 mL ofertada está cubierta. Precio $11.690.</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa 20 mL sin aguja Luer Lock Cranberry, caja 50 unidades</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.traqueo.cl/tienda/insumos/jeringa-20-ml-sin-aguja-luer-lock/</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa 20 mL sin aguja (Luer Lock) | Estéril Cranberry</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Traqueo (traqueo.cl)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>CRANBERRY (Jeringa hipodérmica, sin aguja, estéril, para un solo uso, luer lock)</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>DM 624/24</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>[Pasada complementaria del 11-09-2026] Marca Cranberry declarada explícitamente. DM 624/24 ampara exactamente 20mL Luer Lock sin aguja. Precio $9.500, caja de 50 unidades.</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa Sin Aguja Catéter 60ml (marca comercial Reutter)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>https://farmaciaelquimico.cl/products/jeringa-sin-aguja-cateter-60ml</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa Sin Aguja Cateter 60ml</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Farmacia El Químico (farmaciaelquimico.cl)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>CRANBERRY (Jeringa hipodérmica, estéril, para un uso, Punta Catéter)</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>DM 531/21</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>[Pasada complementaria del 11-09-2026] La publicación declara marca «Reutter», que no figura en el listado. Reutter S.A. es distribuidor de la marca Cranberry (confirmado en otra fiscalización de esta misma sesión, categoría guantes quirúrgicos), y DM 531/21 ampara exactamente 60mL punta catéter. Es muy probable que el producto real sea Cranberry. VERIFICAR EL ENVASE por imagen antes de resolver: es el mismo patrón de «Reutter = distribuidor, no fabricante» detectado el 02-09-2026. Precio $990.</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -898,7 +1326,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre de DM ofertado</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Oferente</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Clasificación</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Jeringa Luer Lock 10cc 21G X 1 1/2 Caja 100 Un. Prosyr</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://afchilespa.cl/producto/jeringa-luer-lock-10cc-21g-x-1-1-2-caja-100-un-prosyr/</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AF Chile SPA</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Marca 'Prosyr' no figura en el listado ISP de jeringas hipodérmicas. Publicación individual identificada por buscador; el acceso directo a la ficha devolvió 403 (protección anti-bot del sitio), datos tomados del título indexado y confirmados por el mismo patrón de marca en otras dos publicaciones de Prosyr (20cc AF Chile SPA y 60mL OSM Ltda) que sí se pudieron verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa Luer Slip 20cc 21G X 1 1/2 Caja 50 Un. Prosyr</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>https://afchilespa.cl/producto/jeringa-luer-slip-20cc-21g-x-1-1-2-caja-50-un-prosyr/</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>AF Chile SPA</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>NO REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Marca 'Prosyr' no figura en el listado ISP de jeringas hipodérmicas. Acceso directo a la ficha bloqueado (403); datos tomados del título indexado por el buscador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Jeringa 20cc Sin Aguja Nedflex (Luer Lock / Luer Slip)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://dipromed.cl/medicina/200-277-jeringa-20-cc-sin-aguja.html</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Dipromed (Chile)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Marca NEDFLEX y presentación de 20 mL (ambos conectores, Luer Lock y Luer Slip) están amparadas por los registros DM 416/16 y DM 456/18 respectivamente, ambos con titular Dipromed S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Jeringa BD Luer Lock 60 ml sin aguja - Caja 60 unidades</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>https://vidamedica.cl/productos/jeringa-bd-luer-lock-60-ml-sin-aguja-caja-60-unidades/</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Vidamedica (Schonfeldt Vidamedica SpA)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Marca Becton Dickinson y volumen de 60 mL coinciden con el registro DM/10JE/0192/09, aunque ese registro especifica 'Punta Catéter' y la publicación declara 'Luer Lock'. Se sugiere que el inspector verifique el tipo de punta exacto contra la ficha técnica antes de confirmar, dado que BD tiene múltiples registros con distintos tipos de punta para volúmenes similares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Estas 4 ofertas se detectaron en la misma búsqueda pero quedaron fuera del reporte por el tope de 10 hallazgos. NO requieren revisión esta semana. Al no quedar registradas como evaluadas, vuelven a considerarse en la próxima corrida de la categoría.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -955,63 +1546,96 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>https://listado.mercadolibre.cl/jeringas-hipodermica-con-aguja</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>jeringas hipodérmicas mercadolibre.cl; jumala jeringa Chile fabricante</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Jumala (no figura en listado ISP — confirmada NO REGISTRADO vía tienda propia del importador, ver hoja principal), Sensimedical/Sensil Medical (no figura en listado ISP, pendiente de verificación manual)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>No determinada (bloqueo 403 en fetch directo de fichas)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Tres publicaciones específicas de marca Jumala detectadas mediante feedback del inspector de la corrida anterior, no accesibles por bloqueo de robots.txt: https://www.mercadolibre.cl/jeringa-desechable-luer-slip-de-10ml-con-aguja-21g-jumala-caja-de-100/p/MLC61663455 ; https://www.mercadolibre.cl/jeringa-desechable-luer-lock-jumala-20cc-21g-x-1-12-20-ml/p/MLC68828424 ; https://www.mercadolibre.cl/pack-x100-jeringa-3ml-con-aguja-21g-jeringa-esteril-caguja/up/MLCU3858403626 . La marca Jumala ya quedó confirmada como NO REGISTRADO mediante una publicación accesible del mismo importador (Importadora AMG), por lo que estas tres publicaciones son evidencia adicional del mismo patrón; se recomienda revisión manual directa para ampliar el universo de casos si el inspector lo estima necesario. Marca Sensimedical detectada en resultados de búsqueda para jeringas 3ml 21G, no verificada contra el listado ISP por bloqueo de acceso.</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Libre Chile</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>https://listado.mercadolibre.cl/jeringas-desechables-sin-aguja</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>jeringas desechables sin aguja / jeringa 20ml / jeringa 60ml</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>No verificable: el sitio responde 403 al acceso automatizado</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>no disponible</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Mercado Libre sigue bloqueando el acceso automatizado a publicaciones individuales. Revisar a mano, con foco en ofertas de venta al público de jeringas de 20-60 mL sin marca o de fabricantes no listados.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>[Pasada complementaria del 11-09-2026] Mercado Libre sigue bloqueando el acceso automatizado a publicaciones individuales. Revisar a mano, con foco en ofertas de venta al público de jeringas de 20-60 mL sin marca o de fabricantes no listados.</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>(no aplica) Fuera de alcance por uso no médico</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>https://www.apicola.cl/producto/jeringa-desechable-50-cc-sin-aguja/</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>jeringa sin aguja apicultura</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>sin marca</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>3 publicaciones (5cc, 20cc, 50cc)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>NO es hallazgo. Agro Apicultura vende jeringas sin aguja como insumo de manejo apícola (alimentación/medicación de colmenas), no como dispositivo médico de uso humano. El registro sanitario ISP regula dispositivos médicos para salud humana; este canal queda fuera de ese alcance por el uso declarado del producto, no por el producto en sí. Se deja anotado para no revisarlo de nuevo.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>[Pasada complementaria del 11-09-2026] NO es hallazgo. Agro Apicultura vende jeringas sin aguja como insumo de manejo apícola (alimentación/medicación de colmenas), no como dispositivo médico de uso humano. El registro sanitario ISP regula dispositivos médicos para salud humana; este canal queda fuera de ese alcance por el uso declarado del producto, no por el producto en sí. Se deja anotado para no revisarlo de nuevo.</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
